--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>24％なら月額+282円</t>
+          <t>24％なら月額+281円</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>※ 幅は、標準給付費3年計3,101,160千円・地域支援事業費191,749千円・補正後被保険者数9,798人・予定収納率99.35％のもとでの保険料基準額（月額6,224円）からの変化。</t>
+          <t>※ 幅は、標準給付費3年計3,093,948千円・地域支援事業費191,749千円・補正後被保険者数9,798人・予定収納率99.35％のもとでの保険料基準額（月額6,210円）からの変化。</t>
         </is>
       </c>
     </row>
@@ -2025,13 +2025,13 @@
         <v>45.8</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>43.8</v>
+        <v>43.6</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>98</v>
@@ -2085,13 +2085,13 @@
         <v>40.8</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>58</v>
@@ -2941,10 +2941,10 @@
         <v>1019104</v>
       </c>
       <c r="C11" s="48" t="n">
-        <v>961669</v>
+        <v>960695</v>
       </c>
       <c r="D11" s="48" t="n">
-        <v>-57435</v>
+        <v>-58408</v>
       </c>
     </row>
     <row r="12">
@@ -2957,10 +2957,10 @@
         <v>1016139</v>
       </c>
       <c r="C12" s="48" t="n">
-        <v>958871</v>
+        <v>956645</v>
       </c>
       <c r="D12" s="48" t="n">
-        <v>-57268</v>
+        <v>-59494</v>
       </c>
     </row>
     <row r="13">
@@ -2973,10 +2973,10 @@
         <v>1013175</v>
       </c>
       <c r="C13" s="48" t="n">
-        <v>956074</v>
+        <v>952595</v>
       </c>
       <c r="D13" s="48" t="n">
-        <v>-57101</v>
+        <v>-60580</v>
       </c>
     </row>
     <row r="14">
@@ -2989,10 +2989,10 @@
         <v>3048418</v>
       </c>
       <c r="C14" s="48" t="n">
-        <v>2876614</v>
+        <v>2869936</v>
       </c>
       <c r="D14" s="48" t="n">
-        <v>-171804</v>
+        <v>-178482</v>
       </c>
     </row>
     <row r="15">
@@ -3005,10 +3005,10 @@
         <v>3286398</v>
       </c>
       <c r="C15" s="48" t="n">
-        <v>3101160</v>
+        <v>3093948</v>
       </c>
       <c r="D15" s="48" t="n">
-        <v>-185237</v>
+        <v>-192449</v>
       </c>
     </row>
     <row r="16">
@@ -3021,10 +3021,10 @@
         <v>6570</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>6224</v>
+        <v>6210</v>
       </c>
       <c r="D16" s="48" t="n">
-        <v>-347</v>
+        <v>-360</v>
       </c>
     </row>
     <row r="17">
@@ -3065,7 +3065,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>※ 自然体推計は、令和8年度を基点とし第1号被保険者1人当たりの給付費を据え置いて人口で延ばしたもの。**見える化システムの自然体推計（利用率・1人1月あたり給付費の変化を0とする）と同じ構造である。**</t>
+          <t>※ 自然体推計は、令和8年度を基点とし第1号被保険者1人当たりの給付費を据え置いて人口で延ばしたもの。**見える化システムの自然体推計（利用率・1人1月あたり給付費の変化を0とする）と総額の置き方が同じである。ただし区分別の延ばし方は異なり、見える化は施設を利用者数一定とする。差は3年計6,678千円・月額13円**（見込量算定の再検証を参照）。</t>
         </is>
       </c>
     </row>
@@ -9464,13 +9464,13 @@
         <v>792</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
@@ -9491,13 +9491,13 @@
         <v>51.2</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="9" t="inlineStr"/>
@@ -9512,13 +9512,13 @@
       </c>
       <c r="D5" s="18" t="n"/>
       <c r="E5" s="7" t="n">
-        <v>28461</v>
+        <v>28333</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>28378</v>
+        <v>28114</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>28295</v>
+        <v>27895</v>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
         <v>4.6</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
@@ -9591,13 +9591,13 @@
       </c>
       <c r="D8" s="18" t="n"/>
       <c r="E8" s="7" t="n">
-        <v>3033</v>
+        <v>3020</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3024</v>
+        <v>2996</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>3016</v>
+        <v>2973</v>
       </c>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="9" t="inlineStr"/>
@@ -9622,13 +9622,13 @@
         <v>273</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -9649,13 +9649,13 @@
         <v>41.8</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>39.9</v>
+        <v>39.5</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>39.8</v>
+        <v>39.2</v>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="9" t="inlineStr"/>
@@ -9670,13 +9670,13 @@
       </c>
       <c r="D11" s="18" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>19314</v>
+        <v>19227</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>19258</v>
+        <v>19078</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>19201</v>
+        <v>18930</v>
       </c>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr"/>
@@ -9783,10 +9783,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -9805,13 +9805,13 @@
       </c>
       <c r="D16" s="18" t="n"/>
       <c r="E16" s="7" t="n">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr"/>
@@ -9836,13 +9836,13 @@
         <v>1531</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1461</v>
+        <v>1447</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1456</v>
+        <v>1436</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -9863,13 +9863,13 @@
         <v>167.5</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>160.3</v>
+        <v>159.5</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>159.8</v>
+        <v>158.3</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>159.3</v>
+        <v>157.1</v>
       </c>
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="9" t="inlineStr"/>
@@ -9884,13 +9884,13 @@
       </c>
       <c r="D19" s="18" t="n"/>
       <c r="E19" s="7" t="n">
-        <v>145895</v>
+        <v>145240</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>145471</v>
+        <v>144118</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>145046</v>
+        <v>142996</v>
       </c>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr"/>
@@ -9915,13 +9915,13 @@
         <v>186</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -9942,13 +9942,13 @@
         <v>26.5</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
       </c>
       <c r="D22" s="18" t="n"/>
       <c r="E22" s="7" t="n">
-        <v>14902</v>
+        <v>14835</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>14858</v>
+        <v>14720</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>14815</v>
+        <v>14606</v>
       </c>
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="9" t="inlineStr"/>
@@ -9994,13 +9994,13 @@
         <v>237</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -10021,13 +10021,13 @@
         <v>25.6</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="9" t="inlineStr"/>
@@ -10042,13 +10042,13 @@
       </c>
       <c r="D25" s="18" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>26209</v>
+        <v>26091</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>26133</v>
+        <v>25890</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>26056</v>
+        <v>25688</v>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" s="9" t="inlineStr"/>
@@ -10106,7 +10106,7 @@
         <v>3.1</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr"/>
@@ -10121,13 +10121,13 @@
       </c>
       <c r="D28" s="18" t="n"/>
       <c r="E28" s="7" t="n">
-        <v>2227</v>
+        <v>2217</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>2220</v>
+        <v>2200</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2214</v>
+        <v>2183</v>
       </c>
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="9" t="inlineStr"/>
@@ -10310,13 +10310,13 @@
         <v>192.8</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>184.5</v>
+        <v>183.7</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>184</v>
+        <v>182.2</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>183.4</v>
+        <v>180.8</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -10335,13 +10335,13 @@
       </c>
       <c r="D36" s="18" t="n"/>
       <c r="E36" s="7" t="n">
-        <v>29951</v>
+        <v>29816</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>29864</v>
+        <v>29586</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>29777</v>
+        <v>29356</v>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="9" t="inlineStr"/>
@@ -10391,13 +10391,13 @@
       </c>
       <c r="D38" s="18" t="n"/>
       <c r="E38" s="7" t="n">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1638</v>
+        <v>1615</v>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="9" t="inlineStr"/>
@@ -10447,13 +10447,13 @@
       </c>
       <c r="D40" s="18" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>1735</v>
+        <v>1727</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1730</v>
+        <v>1713</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1724</v>
+        <v>1700</v>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="9" t="inlineStr"/>
@@ -10503,13 +10503,13 @@
       </c>
       <c r="D42" s="18" t="n"/>
       <c r="E42" s="7" t="n">
-        <v>9299</v>
+        <v>9270</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>9272</v>
+        <v>9211</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>9244</v>
+        <v>9153</v>
       </c>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="9" t="inlineStr"/>
@@ -10534,13 +10534,13 @@
         <v>255</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>244</v>
+        <v>242.9</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>243.3</v>
+        <v>241</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>242.6</v>
+        <v>239.1</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
@@ -10559,13 +10559,13 @@
       </c>
       <c r="D44" s="18" t="n"/>
       <c r="E44" s="7" t="n">
-        <v>46001</v>
+        <v>45794</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>45867</v>
+        <v>45441</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>45733</v>
+        <v>45087</v>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="9" t="inlineStr"/>
@@ -10784,10 +10784,10 @@
         <v>91</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         <v>8.6</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="9" t="inlineStr"/>
@@ -10829,13 +10829,13 @@
       </c>
       <c r="D54" s="18" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>11708</v>
+        <v>11656</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>11674</v>
+        <v>11566</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>11640</v>
+        <v>11476</v>
       </c>
       <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="9" t="inlineStr"/>
@@ -10860,13 +10860,13 @@
         <v>22.2</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="F55" s="13" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
@@ -10885,13 +10885,13 @@
       </c>
       <c r="D56" s="18" t="n"/>
       <c r="E56" s="7" t="n">
-        <v>47434</v>
+        <v>47221</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>47296</v>
+        <v>46857</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>47158</v>
+        <v>46492</v>
       </c>
       <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="9" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         <v>44.6</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>42.4</v>
+        <v>42</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
@@ -10941,13 +10941,13 @@
       </c>
       <c r="D58" s="18" t="n"/>
       <c r="E58" s="7" t="n">
-        <v>128568</v>
+        <v>128169</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>128194</v>
+        <v>127359</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>127820</v>
+        <v>126549</v>
       </c>
       <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="9" t="inlineStr"/>
@@ -11028,13 +11028,13 @@
         <v>40.8</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="F61" s="13" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
@@ -11053,13 +11053,13 @@
       </c>
       <c r="D62" s="18" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>120885</v>
+        <v>121271</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>120533</v>
+        <v>121271</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>120181</v>
+        <v>121271</v>
       </c>
       <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="9" t="inlineStr"/>
@@ -11140,13 +11140,13 @@
         <v>71.09999999999999</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="F65" s="13" t="n">
-        <v>67.8</v>
+        <v>68.2</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>67.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
@@ -11165,13 +11165,13 @@
       </c>
       <c r="D66" s="18" t="n"/>
       <c r="E66" s="7" t="n">
-        <v>195989</v>
+        <v>196616</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>195419</v>
+        <v>196616</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>194849</v>
+        <v>196616</v>
       </c>
       <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="9" t="inlineStr"/>
@@ -11196,13 +11196,13 @@
         <v>27.8</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="F67" s="13" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
@@ -11221,13 +11221,13 @@
       </c>
       <c r="D68" s="18" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>88521</v>
+        <v>88804</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>88264</v>
+        <v>88804</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>88006</v>
+        <v>88804</v>
       </c>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="9" t="inlineStr"/>
@@ -11333,13 +11333,13 @@
       </c>
       <c r="D72" s="18" t="n"/>
       <c r="E72" s="7" t="n">
-        <v>4123</v>
+        <v>4136</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>4111</v>
+        <v>4136</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>4099</v>
+        <v>4136</v>
       </c>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="9" t="inlineStr"/>
@@ -11360,13 +11360,13 @@
         <v>1005.3</v>
       </c>
       <c r="E73" s="21" t="n">
-        <v>961.8</v>
+        <v>958.6</v>
       </c>
       <c r="F73" s="21" t="n">
-        <v>959.1</v>
+        <v>952.3</v>
       </c>
       <c r="G73" s="21" t="n">
-        <v>956.3</v>
+        <v>946</v>
       </c>
       <c r="H73" s="20" t="inlineStr"/>
       <c r="I73" s="22" t="inlineStr">
@@ -11389,13 +11389,13 @@
       </c>
       <c r="D74" s="23" t="n"/>
       <c r="E74" s="24" t="n">
-        <v>926731</v>
+        <v>925910</v>
       </c>
       <c r="F74" s="24" t="n">
-        <v>924035</v>
+        <v>922124</v>
       </c>
       <c r="G74" s="24" t="n">
-        <v>921340</v>
+        <v>918338</v>
       </c>
       <c r="H74" s="20" t="inlineStr"/>
       <c r="I74" s="22" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         <v>31</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -11541,13 +11541,13 @@
         <v>7.6</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F80" s="13" t="n">
         <v>7.2</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" s="9" t="inlineStr"/>
@@ -11562,13 +11562,13 @@
       </c>
       <c r="D81" s="18" t="n"/>
       <c r="E81" s="7" t="n">
-        <v>2118</v>
+        <v>2109</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>2112</v>
+        <v>2092</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>2106</v>
+        <v>2076</v>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr"/>
@@ -11697,13 +11697,13 @@
       </c>
       <c r="D86" s="18" t="n"/>
       <c r="E86" s="7" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" s="9" t="inlineStr"/>
@@ -11728,13 +11728,13 @@
         <v>27</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>25.7</v>
+        <v>25.3</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
@@ -11753,13 +11753,13 @@
       </c>
       <c r="D88" s="18" t="n"/>
       <c r="E88" s="7" t="n">
-        <v>11184</v>
+        <v>11133</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>11151</v>
+        <v>11047</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>11119</v>
+        <v>10961</v>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr"/>
@@ -11832,13 +11832,13 @@
       </c>
       <c r="D91" s="18" t="n"/>
       <c r="E91" s="7" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="9" t="inlineStr"/>
@@ -11914,10 +11914,10 @@
         <v>48</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr"/>
@@ -12100,13 +12100,13 @@
         <v>54.2</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
@@ -12125,13 +12125,13 @@
       </c>
       <c r="D102" s="18" t="n"/>
       <c r="E102" s="7" t="n">
-        <v>5741</v>
+        <v>5715</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>5724</v>
+        <v>5671</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>5707</v>
+        <v>5627</v>
       </c>
       <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="9" t="inlineStr"/>
@@ -12162,7 +12162,7 @@
         <v>2.4</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
@@ -12181,13 +12181,13 @@
       </c>
       <c r="D104" s="18" t="n"/>
       <c r="E104" s="7" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="9" t="inlineStr"/>
@@ -12212,7 +12212,7 @@
         <v>1.8</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F105" s="13" t="n">
         <v>1.7</v>
@@ -12237,13 +12237,13 @@
       </c>
       <c r="D106" s="18" t="n"/>
       <c r="E106" s="7" t="n">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>834</v>
+        <v>822</v>
       </c>
       <c r="H106" s="6" t="inlineStr"/>
       <c r="I106" s="9" t="inlineStr"/>
@@ -12324,13 +12324,13 @@
         <v>74.8</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>71.5</v>
+        <v>71.2</v>
       </c>
       <c r="F109" s="13" t="n">
-        <v>71.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>71.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
@@ -12349,13 +12349,13 @@
       </c>
       <c r="D110" s="18" t="n"/>
       <c r="E110" s="7" t="n">
-        <v>3967</v>
+        <v>3949</v>
       </c>
       <c r="F110" s="7" t="n">
-        <v>3955</v>
+        <v>3918</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>3944</v>
+        <v>3888</v>
       </c>
       <c r="H110" s="6" t="inlineStr"/>
       <c r="I110" s="9" t="inlineStr"/>
@@ -12459,13 +12459,13 @@
         <v>7.1</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F114" s="13" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
@@ -12484,13 +12484,13 @@
       </c>
       <c r="D115" s="18" t="n"/>
       <c r="E115" s="7" t="n">
-        <v>6973</v>
+        <v>6942</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>6953</v>
+        <v>6888</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>6932</v>
+        <v>6834</v>
       </c>
       <c r="H115" s="6" t="inlineStr"/>
       <c r="I115" s="9" t="inlineStr"/>
@@ -12540,13 +12540,13 @@
       </c>
       <c r="D117" s="18" t="n"/>
       <c r="E117" s="7" t="n">
-        <v>3199</v>
+        <v>3189</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>3189</v>
+        <v>3169</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>3180</v>
+        <v>3149</v>
       </c>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="9" t="inlineStr"/>
@@ -12567,13 +12567,13 @@
         <v>179.1</v>
       </c>
       <c r="E118" s="21" t="n">
-        <v>171.3</v>
+        <v>170.6</v>
       </c>
       <c r="F118" s="21" t="n">
-        <v>170.8</v>
+        <v>169.3</v>
       </c>
       <c r="G118" s="21" t="n">
-        <v>170.3</v>
+        <v>167.9</v>
       </c>
       <c r="H118" s="20" t="inlineStr"/>
       <c r="I118" s="22" t="inlineStr">
@@ -12596,13 +12596,13 @@
       </c>
       <c r="D119" s="23" t="n"/>
       <c r="E119" s="24" t="n">
-        <v>34938</v>
+        <v>34785</v>
       </c>
       <c r="F119" s="24" t="n">
-        <v>34836</v>
+        <v>34521</v>
       </c>
       <c r="G119" s="24" t="n">
-        <v>34734</v>
+        <v>34257</v>
       </c>
       <c r="H119" s="20" t="inlineStr"/>
       <c r="I119" s="22" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>67.61313368071588</v>
+        <v>68.22635987852225</v>
       </c>
       <c r="F2" s="14" t="n"/>
       <c r="G2" s="26" t="n">
-        <v>125.2095068161405</v>
+        <v>126.3451108861523</v>
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>26.47454472375041</v>
+        <v>26.71465908490789</v>
       </c>
       <c r="F3" s="14" t="n"/>
       <c r="G3" s="28" t="n"/>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>0.9511812475598951</v>
+        <v>0.9598081108350141</v>
       </c>
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="28" t="n"/>
@@ -12844,11 +12844,11 @@
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>38.83990094202905</v>
+        <v>39.19216452576308</v>
       </c>
       <c r="F5" s="14" t="n"/>
       <c r="G5" s="30" t="n">
-        <v>66.96534645177424</v>
+        <v>67.57269745821219</v>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
@@ -12881,11 +12881,11 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>43.5165420758652</v>
+        <v>43.08374831183189</v>
       </c>
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="30" t="n">
-        <v>44.40463477129102</v>
+        <v>43.96300848146112</v>
       </c>
       <c r="H6" s="29" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>3.80472499023958</v>
+        <v>3.766885098302241</v>
       </c>
       <c r="F7" s="14" t="n"/>
       <c r="G7" s="28" t="n"/>
@@ -12951,13 +12951,13 @@
         </is>
       </c>
       <c r="E8" s="13" t="n">
-        <v>159.3228589662824</v>
+        <v>157.0708325619449</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>56.01908789715729</v>
+        <v>55.22725886578144</v>
       </c>
       <c r="G8" s="30" t="n">
-        <v>40.30150208428582</v>
+        <v>39.73184091063413</v>
       </c>
       <c r="H8" s="29" t="inlineStr">
         <is>
@@ -12988,10 +12988,10 @@
         </is>
       </c>
       <c r="E9" s="13" t="n">
-        <v>50.88819674445439</v>
+        <v>50.16889278844211</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>6.792409678087968</v>
+        <v>6.696399061385634</v>
       </c>
       <c r="G9" s="28" t="n"/>
       <c r="H9" s="29" t="inlineStr">
@@ -13025,13 +13025,13 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>8.560631228039055</v>
+        <v>8.439626824223906</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>3.484615916541538</v>
+        <v>3.435360918834731</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>29.03846597117949</v>
+        <v>28.62800765695609</v>
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>27.90131659509026</v>
+        <v>27.50693187154458</v>
       </c>
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="28" t="n"/>
@@ -13096,14 +13096,14 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>**※ 介護老人福祉施設は町内定員54人に対し見込み67.6人/月で、13.6人が町外の施設の利用にあたる。**第9期の自給率の分析と整合させる。</t>
+          <t>**※ 介護老人福祉施設は町内定員54人に対し見込み68.2人/月で、14.2人が町外の施設の利用にあたる。**第9期の自給率の分析と整合させる。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**※ 小規模多機能型居宅介護は登録定員が29人以下と定められている。**見込み27.9人/月は登録者数にあたるため、1事業所であれば上限を超える。事業所数と登録定員を町に確認する。</t>
+          <t>**※ 小規模多機能型居宅介護は登録定員が29人以下と定められている。**見込み27.5人/月は登録者数にあたるため、1事業所であれば上限を超える。事業所数と登録定員を町に確認する。</t>
         </is>
       </c>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>±1.5％で月額±87円</t>
+          <t>±1.5％で月額±85円</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>24％なら月額+281円</t>
+          <t>24％なら月額+269円</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>6.148％</t>
+          <t>5.533％</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>1ポイント下がると月額+265円</t>
+          <t>1ポイント下がると月額+253円</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>1％で月額+4.2円</t>
+          <t>1％で月額+4.0円</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>12,000千円で月額-103円、35,000千円で月額-300円</t>
+          <t>12,000千円で月額-98円、35,000千円で月額-287円</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>※ 幅は、標準給付費3年計3,093,948千円・地域支援事業費191,749千円・補正後被保険者数9,798人・予定収納率99.35％のもとでの保険料基準額（月額6,210円）からの変化。</t>
+          <t>※ 幅は、標準給付費3年計3,093,948千円・地域支援事業費191,749千円・補正後被保険者数10,245人・予定収納率99.35％のもとでの保険料基準額（月額6,095円）からの変化。</t>
         </is>
       </c>
     </row>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="B16" s="48" t="n">
-        <v>6570</v>
+        <v>6449</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>6210</v>
+        <v>6095</v>
       </c>
       <c r="D16" s="48" t="n">
-        <v>-360</v>
+        <v>-354</v>
       </c>
     </row>
     <row r="17">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B17" s="48" t="n">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="C17" s="48" t="n">
-        <v>6300</v>
+        <v>6100</v>
       </c>
       <c r="D17" s="48" t="n"/>
     </row>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>1ポイント下がると月額+253円</t>
+          <t>1ポイント下がると月額+262円</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>1％で月額+4.0円</t>
+          <t>1％で月額+3.6円</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>※ 幅は、標準給付費3年計3,093,948千円・地域支援事業費191,749千円・補正後被保険者数10,245人・予定収納率99.35％のもとでの保険料基準額（月額6,095円）からの変化。</t>
+          <t>※ 幅は、標準給付費3年計3,093,948千円・地域支援事業費191,749千円・補正後被保険者数10,245人・予定収納率99.35％のもとでの保険料基準額（月額6,048円）からの変化。</t>
         </is>
       </c>
     </row>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="B16" s="48" t="n">
-        <v>6449</v>
+        <v>6402</v>
       </c>
       <c r="C16" s="48" t="n">
-        <v>6095</v>
+        <v>6048</v>
       </c>
       <c r="D16" s="48" t="n">
         <v>-354</v>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>町内定員（令和7年度）</t>
+          <t>町内定員（令和6年度）</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_サービス見込量_20260925.xlsx
@@ -1791,17 +1791,17 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>**年報 様式4 の保有額は令和5・6年度末とも12,000千円だが、令和4年度末は120,000千円で、繰入金は全年度ゼロなのに残高が10分の1になっており系列に矛盾がある。**正しい残高が分からないため取崩を見込まない</t>
+          <t>**残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円。**取崩額は町と協議会で決めるため、標準では見込まない</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>12,000千円で月額-98円、35,000千円で月額-287円</t>
+          <t>105,000千円で月額-860円、35,000千円で月額-287円</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>基金運用状況調書（町）</t>
+          <t>財産に関する調書（町。令和7年度末）</t>
         </is>
       </c>
     </row>
